--- a/fake data/04_Course_Catalog.xlsx
+++ b/fake data/04_Course_Catalog.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R746c937093474c75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Course Catalog" sheetId="2" r:id="R4837be28d80d406f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Major Course Map" sheetId="3" r:id="R8820e06711064ac0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shared Courses" sheetId="4" r:id="Rb949fce4145c4419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" r:id="Rfaf4ef6759fa427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Rce729d9d7f254085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Course Catalog" sheetId="2" r:id="R7ee7577914714038"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Major Course Map" sheetId="3" r:id="Rd5874b31091c4a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Shared Courses" sheetId="4" r:id="Rc3a7030b1d204602"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" r:id="R1e6e394f5dac49ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -105,7 +105,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="21">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -137,6 +137,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -148,7 +151,7 @@
         <x:color rgb="FF17365D"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDDEBF7"/>
         </x:patternFill>
       </x:fill>
@@ -158,7 +161,7 @@
         <x:color rgb="FF595959"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF2F2F2"/>
         </x:patternFill>
       </x:fill>
@@ -366,7 +369,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6127dfc3b4524234"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R940a6210461746bd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -861,7 +864,7 @@
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
       <x:c r="A24" s="19" t="str">
-        <x:v>Shared lectures may combine majors. Tutorials and labs are always scheduled separately by major and cohort group.</x:v>
+        <x:v>Only lectures may combine majors. Tutorials and labs must be scheduled separately for one major and one cohort group.</x:v>
       </x:c>
       <x:c r="B24" s="19"/>
       <x:c r="C24" s="19"/>
@@ -883,7 +886,7 @@
     <x:mergeCell ref="A24:K24"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba3f07a042fc4688"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R366610d6fe7f4b2c"/>
 </x:worksheet>
 </file>
 
@@ -897,8 +900,8 @@
     <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="9" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="15" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="52" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="20" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="10" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="20" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
@@ -954,13 +957,13 @@
         <x:v>Year</x:v>
       </x:c>
       <x:c r="F4" s="20" t="str">
-        <x:v>Shared Course</x:v>
+        <x:v>Shared Lecture</x:v>
       </x:c>
       <x:c r="G4" s="20" t="str">
-        <x:v>Majors Covered</x:v>
+        <x:v>Majors Sharing Lecture</x:v>
       </x:c>
       <x:c r="H4" s="20" t="str">
-        <x:v>Support Mode</x:v>
+        <x:v>Major-only Support</x:v>
       </x:c>
       <x:c r="I4" s="20" t="str">
         <x:v>Credits</x:v>
@@ -11816,7 +11819,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R186f882af91b4acd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb34f8f16239452c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11917,7 +11920,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I5" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
@@ -11946,7 +11949,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I6" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
@@ -11975,7 +11978,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I7" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
@@ -12004,7 +12007,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I8" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
@@ -12033,7 +12036,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I9" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="20" customHeight="1">
@@ -12062,7 +12065,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I10" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="20" customHeight="1">
@@ -12091,7 +12094,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I11" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20" customHeight="1">
@@ -12120,7 +12123,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I12" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="20" customHeight="1">
@@ -12149,7 +12152,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I13" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="20" customHeight="1">
@@ -12178,7 +12181,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I14" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="20" customHeight="1">
@@ -12207,7 +12210,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I15" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="20" customHeight="1">
@@ -12236,7 +12239,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I16" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="20" customHeight="1">
@@ -12265,7 +12268,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I17" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="20" customHeight="1">
@@ -12294,7 +12297,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I18" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="20" customHeight="1">
@@ -12323,7 +12326,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I19" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="20" customHeight="1">
@@ -12352,7 +12355,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I20" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="20" customHeight="1">
@@ -12381,7 +12384,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I21" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="20" customHeight="1">
@@ -12410,7 +12413,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I22" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="20" customHeight="1">
@@ -12439,7 +12442,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I23" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="20" customHeight="1">
@@ -12468,7 +12471,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I24" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="20" customHeight="1">
@@ -12497,7 +12500,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I25" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="20" customHeight="1">
@@ -12526,7 +12529,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I26" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="20" customHeight="1">
@@ -12555,7 +12558,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I27" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="20" customHeight="1">
@@ -12584,7 +12587,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I28" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="20" customHeight="1">
@@ -12613,7 +12616,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I29" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="20" customHeight="1">
@@ -12642,7 +12645,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I30" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="20" customHeight="1">
@@ -12671,7 +12674,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I31" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="20" customHeight="1">
@@ -12700,7 +12703,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I32" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="20" customHeight="1">
@@ -12729,7 +12732,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I33" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="20" customHeight="1">
@@ -12758,7 +12761,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I34" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="20" customHeight="1">
@@ -12787,7 +12790,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I35" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="20" customHeight="1">
@@ -12816,7 +12819,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I36" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="20" customHeight="1">
@@ -12845,7 +12848,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I37" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="20" customHeight="1">
@@ -12874,7 +12877,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I38" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="20" customHeight="1">
@@ -12903,7 +12906,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I39" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="20" customHeight="1">
@@ -12932,7 +12935,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I40" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="20" customHeight="1">
@@ -12961,7 +12964,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I41" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="20" customHeight="1">
@@ -12990,7 +12993,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I42" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="20" customHeight="1">
@@ -13019,7 +13022,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I43" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="20" customHeight="1">
@@ -13048,7 +13051,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I44" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="20" customHeight="1">
@@ -13077,7 +13080,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I45" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="20" customHeight="1">
@@ -13106,7 +13109,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I46" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="20" customHeight="1">
@@ -13135,7 +13138,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I47" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="20" customHeight="1">
@@ -13164,7 +13167,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I48" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="20" customHeight="1">
@@ -13193,7 +13196,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I49" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="20" customHeight="1">
@@ -13222,7 +13225,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I50" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="20" customHeight="1">
@@ -13251,7 +13254,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I51" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="20" customHeight="1">
@@ -13280,7 +13283,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I52" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="20" customHeight="1">
@@ -13309,7 +13312,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I53" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="20" customHeight="1">
@@ -13338,7 +13341,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I54" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="20" customHeight="1">
@@ -13367,7 +13370,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I55" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="20" customHeight="1">
@@ -13396,7 +13399,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I56" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="20" customHeight="1">
@@ -13425,7 +13428,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I57" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="20" customHeight="1">
@@ -13454,7 +13457,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I58" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="20" customHeight="1">
@@ -13483,7 +13486,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I59" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="20" customHeight="1">
@@ -13512,7 +13515,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I60" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="20" customHeight="1">
@@ -13541,7 +13544,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I61" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="20" customHeight="1">
@@ -13570,7 +13573,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I62" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="20" customHeight="1">
@@ -13599,7 +13602,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I63" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="20" customHeight="1">
@@ -13628,7 +13631,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I64" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="20" customHeight="1">
@@ -13657,7 +13660,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I65" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="20" customHeight="1">
@@ -13686,7 +13689,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I66" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="20" customHeight="1">
@@ -13715,7 +13718,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I67" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="20" customHeight="1">
@@ -13744,7 +13747,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I68" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="20" customHeight="1">
@@ -13773,7 +13776,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I69" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="20" customHeight="1">
@@ -13802,7 +13805,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I70" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="20" customHeight="1">
@@ -13831,7 +13834,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I71" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="20" customHeight="1">
@@ -13860,7 +13863,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I72" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="20" customHeight="1">
@@ -13889,7 +13892,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I73" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="20" customHeight="1">
@@ -13918,7 +13921,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I74" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="20" customHeight="1">
@@ -13947,7 +13950,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I75" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="20" customHeight="1">
@@ -13976,7 +13979,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I76" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="20" customHeight="1">
@@ -14005,7 +14008,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I77" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="20" customHeight="1">
@@ -14034,7 +14037,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I78" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="20" customHeight="1">
@@ -14063,7 +14066,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I79" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="20" customHeight="1">
@@ -14092,7 +14095,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I80" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="20" customHeight="1">
@@ -14121,7 +14124,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I81" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="20" customHeight="1">
@@ -14150,7 +14153,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I82" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="20" customHeight="1">
@@ -14179,7 +14182,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I83" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="20" customHeight="1">
@@ -14208,7 +14211,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I84" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="20" customHeight="1">
@@ -14237,7 +14240,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I85" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="20" customHeight="1">
@@ -14266,7 +14269,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I86" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="20" customHeight="1">
@@ -14295,7 +14298,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I87" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="20" customHeight="1">
@@ -14324,7 +14327,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I88" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="20" customHeight="1">
@@ -14353,7 +14356,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I89" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="20" customHeight="1">
@@ -14382,7 +14385,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I90" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="20" customHeight="1">
@@ -14411,7 +14414,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I91" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="20" customHeight="1">
@@ -14440,7 +14443,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I92" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="20" customHeight="1">
@@ -14469,7 +14472,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I93" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="20" customHeight="1">
@@ -14498,7 +14501,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I94" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="20" customHeight="1">
@@ -14527,7 +14530,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I95" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="20" customHeight="1">
@@ -14556,7 +14559,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I96" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="20" customHeight="1">
@@ -14585,7 +14588,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I97" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="20" customHeight="1">
@@ -14614,7 +14617,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I98" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="20" customHeight="1">
@@ -14643,7 +14646,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I99" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="20" customHeight="1">
@@ -14672,7 +14675,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I100" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="20" customHeight="1">
@@ -14701,7 +14704,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I101" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="20" customHeight="1">
@@ -14730,7 +14733,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I102" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="20" customHeight="1">
@@ -14759,7 +14762,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I103" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="20" customHeight="1">
@@ -14788,7 +14791,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I104" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="20" customHeight="1">
@@ -14817,7 +14820,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I105" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="20" customHeight="1">
@@ -14846,7 +14849,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I106" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="20" customHeight="1">
@@ -14875,7 +14878,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I107" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="20" customHeight="1">
@@ -14904,7 +14907,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I108" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="20" customHeight="1">
@@ -14933,7 +14936,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I109" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="20" customHeight="1">
@@ -14962,7 +14965,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I110" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="20" customHeight="1">
@@ -14991,7 +14994,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I111" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="20" customHeight="1">
@@ -15020,7 +15023,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I112" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="20" customHeight="1">
@@ -15049,7 +15052,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I113" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="20" customHeight="1">
@@ -15078,7 +15081,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I114" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="20" customHeight="1">
@@ -15107,7 +15110,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I115" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="20" customHeight="1">
@@ -15136,7 +15139,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I116" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="20" customHeight="1">
@@ -15165,7 +15168,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I117" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="20" customHeight="1">
@@ -15194,7 +15197,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I118" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="20" customHeight="1">
@@ -15223,7 +15226,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I119" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="120" ht="20" customHeight="1">
@@ -15252,7 +15255,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I120" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="121" ht="20" customHeight="1">
@@ -15281,7 +15284,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I121" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="122" ht="20" customHeight="1">
@@ -15310,7 +15313,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I122" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="123" ht="20" customHeight="1">
@@ -15339,7 +15342,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I123" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="124" ht="20" customHeight="1">
@@ -15368,7 +15371,7 @@
         <x:v>May combine faculty majors</x:v>
       </x:c>
       <x:c r="I124" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="125" ht="20" customHeight="1">
@@ -15397,7 +15400,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I125" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="126" ht="20" customHeight="1">
@@ -15426,7 +15429,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I126" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="127" ht="20" customHeight="1">
@@ -15455,7 +15458,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I127" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="128" ht="20" customHeight="1">
@@ -15484,7 +15487,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I128" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="129" ht="20" customHeight="1">
@@ -15513,7 +15516,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I129" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="130" ht="20" customHeight="1">
@@ -15542,7 +15545,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I130" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="131" ht="20" customHeight="1">
@@ -15571,7 +15574,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I131" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="132" ht="20" customHeight="1">
@@ -15600,7 +15603,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I132" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="133" ht="20" customHeight="1">
@@ -15629,7 +15632,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I133" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="134" ht="20" customHeight="1">
@@ -15658,7 +15661,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I134" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="135" ht="20" customHeight="1">
@@ -15687,7 +15690,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I135" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="136" ht="20" customHeight="1">
@@ -15716,7 +15719,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I136" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="137" ht="20" customHeight="1">
@@ -15745,7 +15748,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I137" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="138" ht="20" customHeight="1">
@@ -15774,7 +15777,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I138" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="139" ht="20" customHeight="1">
@@ -15803,7 +15806,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I139" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="140" ht="20" customHeight="1">
@@ -15832,7 +15835,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I140" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="141" ht="20" customHeight="1">
@@ -15861,7 +15864,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I141" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="142" ht="20" customHeight="1">
@@ -15890,7 +15893,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I142" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="143" ht="20" customHeight="1">
@@ -15919,7 +15922,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I143" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="144" ht="20" customHeight="1">
@@ -15948,7 +15951,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I144" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="145" ht="20" customHeight="1">
@@ -15977,7 +15980,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I145" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="146" ht="20" customHeight="1">
@@ -16006,7 +16009,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I146" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="147" ht="20" customHeight="1">
@@ -16035,7 +16038,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I147" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="148" ht="20" customHeight="1">
@@ -16064,7 +16067,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I148" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="149" ht="20" customHeight="1">
@@ -16093,7 +16096,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I149" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="150" ht="20" customHeight="1">
@@ -16122,7 +16125,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I150" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="151" ht="20" customHeight="1">
@@ -16151,7 +16154,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I151" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="152" ht="20" customHeight="1">
@@ -16180,7 +16183,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I152" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="153" ht="20" customHeight="1">
@@ -16209,7 +16212,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I153" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="154" ht="20" customHeight="1">
@@ -16238,7 +16241,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I154" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="155" ht="20" customHeight="1">
@@ -16267,7 +16270,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I155" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="156" ht="20" customHeight="1">
@@ -16296,7 +16299,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I156" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="157" ht="20" customHeight="1">
@@ -16325,7 +16328,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I157" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="158" ht="20" customHeight="1">
@@ -16354,7 +16357,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I158" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="159" ht="20" customHeight="1">
@@ -16383,7 +16386,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I159" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="160" ht="20" customHeight="1">
@@ -16412,7 +16415,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I160" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="161" ht="20" customHeight="1">
@@ -16441,7 +16444,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I161" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="162" ht="20" customHeight="1">
@@ -16470,7 +16473,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I162" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="163" ht="20" customHeight="1">
@@ -16499,7 +16502,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I163" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="164" ht="20" customHeight="1">
@@ -16528,7 +16531,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I164" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="165" ht="20" customHeight="1">
@@ -16557,7 +16560,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I165" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="166" ht="20" customHeight="1">
@@ -16586,7 +16589,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I166" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="167" ht="20" customHeight="1">
@@ -16615,7 +16618,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I167" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="168" ht="20" customHeight="1">
@@ -16644,7 +16647,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I168" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="169" ht="20" customHeight="1">
@@ -16673,7 +16676,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I169" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="170" ht="20" customHeight="1">
@@ -16702,7 +16705,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I170" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="171" ht="20" customHeight="1">
@@ -16731,7 +16734,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I171" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="172" ht="20" customHeight="1">
@@ -16760,7 +16763,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I172" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="173" ht="20" customHeight="1">
@@ -16789,7 +16792,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I173" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="174" ht="20" customHeight="1">
@@ -16818,7 +16821,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I174" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="175" ht="20" customHeight="1">
@@ -16847,7 +16850,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I175" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="176" ht="20" customHeight="1">
@@ -16876,7 +16879,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I176" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="177" ht="20" customHeight="1">
@@ -16905,7 +16908,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I177" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="178" ht="20" customHeight="1">
@@ -16934,7 +16937,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I178" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="179" ht="20" customHeight="1">
@@ -16963,7 +16966,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I179" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="180" ht="20" customHeight="1">
@@ -16992,7 +16995,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I180" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="181" ht="20" customHeight="1">
@@ -17021,7 +17024,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I181" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="182" ht="20" customHeight="1">
@@ -17050,7 +17053,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I182" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="183" ht="20" customHeight="1">
@@ -17079,7 +17082,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I183" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="184" ht="20" customHeight="1">
@@ -17108,7 +17111,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I184" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="185" ht="20" customHeight="1">
@@ -17137,7 +17140,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I185" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="186" ht="20" customHeight="1">
@@ -17166,7 +17169,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I186" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="20" customHeight="1">
@@ -17195,7 +17198,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I187" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="20" customHeight="1">
@@ -17224,7 +17227,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I188" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="20" customHeight="1">
@@ -17253,7 +17256,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I189" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="190" ht="20" customHeight="1">
@@ -17282,7 +17285,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I190" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="191" ht="20" customHeight="1">
@@ -17311,7 +17314,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I191" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="192" ht="20" customHeight="1">
@@ -17340,7 +17343,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I192" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="193" ht="20" customHeight="1">
@@ -17369,7 +17372,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I193" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="20" customHeight="1">
@@ -17398,7 +17401,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I194" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="20" customHeight="1">
@@ -17427,7 +17430,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I195" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="20" customHeight="1">
@@ -17456,7 +17459,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I196" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="20" customHeight="1">
@@ -17485,7 +17488,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I197" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="20" customHeight="1">
@@ -17514,7 +17517,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I198" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="20" customHeight="1">
@@ -17543,7 +17546,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I199" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="20" customHeight="1">
@@ -17572,7 +17575,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I200" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="201" ht="20" customHeight="1">
@@ -17601,7 +17604,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I201" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="202" ht="20" customHeight="1">
@@ -17630,7 +17633,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I202" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="20" customHeight="1">
@@ -17659,7 +17662,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I203" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="204" ht="20" customHeight="1">
@@ -17688,7 +17691,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I204" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="205" ht="20" customHeight="1">
@@ -17717,7 +17720,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I205" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="206" ht="20" customHeight="1">
@@ -17746,7 +17749,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I206" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="207" ht="20" customHeight="1">
@@ -17775,7 +17778,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I207" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="208" ht="20" customHeight="1">
@@ -17804,7 +17807,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I208" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="209" ht="20" customHeight="1">
@@ -17833,7 +17836,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I209" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="210" ht="20" customHeight="1">
@@ -17862,7 +17865,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I210" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="211" ht="20" customHeight="1">
@@ -17891,7 +17894,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I211" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="212" ht="20" customHeight="1">
@@ -17920,7 +17923,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I212" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="213" ht="20" customHeight="1">
@@ -17949,7 +17952,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I213" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="214" ht="20" customHeight="1">
@@ -17978,7 +17981,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I214" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="215" ht="20" customHeight="1">
@@ -18007,7 +18010,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I215" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="216" ht="20" customHeight="1">
@@ -18036,7 +18039,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I216" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="217" ht="20" customHeight="1">
@@ -18065,7 +18068,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I217" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="218" ht="20" customHeight="1">
@@ -18094,7 +18097,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I218" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="219" ht="20" customHeight="1">
@@ -18123,7 +18126,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I219" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="220" ht="20" customHeight="1">
@@ -18152,7 +18155,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I220" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="221" ht="20" customHeight="1">
@@ -18181,7 +18184,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I221" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="222" ht="20" customHeight="1">
@@ -18210,7 +18213,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I222" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="223" ht="20" customHeight="1">
@@ -18239,7 +18242,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I223" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="224" ht="20" customHeight="1">
@@ -18268,7 +18271,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I224" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="225" ht="20" customHeight="1">
@@ -18297,7 +18300,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I225" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="226" ht="20" customHeight="1">
@@ -18326,7 +18329,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I226" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="227" ht="20" customHeight="1">
@@ -18355,7 +18358,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I227" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="228" ht="20" customHeight="1">
@@ -18384,7 +18387,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I228" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="229" ht="20" customHeight="1">
@@ -18413,7 +18416,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I229" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="230" ht="20" customHeight="1">
@@ -18442,7 +18445,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I230" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="231" ht="20" customHeight="1">
@@ -18471,7 +18474,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I231" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="232" ht="20" customHeight="1">
@@ -18500,7 +18503,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I232" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="233" ht="20" customHeight="1">
@@ -18529,7 +18532,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I233" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="234" ht="20" customHeight="1">
@@ -18558,7 +18561,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I234" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="235" ht="20" customHeight="1">
@@ -18587,7 +18590,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I235" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="236" ht="20" customHeight="1">
@@ -18616,7 +18619,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I236" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="237" ht="20" customHeight="1">
@@ -18645,7 +18648,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I237" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="238" ht="20" customHeight="1">
@@ -18674,7 +18677,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I238" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="239" ht="20" customHeight="1">
@@ -18703,7 +18706,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I239" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="240" ht="20" customHeight="1">
@@ -18732,7 +18735,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I240" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="241" ht="20" customHeight="1">
@@ -18761,7 +18764,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I241" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="242" ht="20" customHeight="1">
@@ -18790,7 +18793,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I242" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="243" ht="20" customHeight="1">
@@ -18819,7 +18822,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I243" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="244" ht="20" customHeight="1">
@@ -18848,7 +18851,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I244" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="245" ht="20" customHeight="1">
@@ -18877,7 +18880,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I245" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="246" ht="20" customHeight="1">
@@ -18906,7 +18909,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I246" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="247" ht="20" customHeight="1">
@@ -18935,7 +18938,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I247" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="248" ht="20" customHeight="1">
@@ -18964,7 +18967,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I248" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="249" ht="20" customHeight="1">
@@ -18993,7 +18996,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I249" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="250" ht="20" customHeight="1">
@@ -19022,7 +19025,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I250" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="251" ht="20" customHeight="1">
@@ -19051,7 +19054,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I251" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="252" ht="20" customHeight="1">
@@ -19080,7 +19083,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I252" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="253" ht="20" customHeight="1">
@@ -19109,7 +19112,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I253" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="254" ht="20" customHeight="1">
@@ -19138,7 +19141,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I254" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="255" ht="20" customHeight="1">
@@ -19167,7 +19170,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I255" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="256" ht="20" customHeight="1">
@@ -19196,7 +19199,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I256" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="257" ht="20" customHeight="1">
@@ -19225,7 +19228,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I257" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="258" ht="20" customHeight="1">
@@ -19254,7 +19257,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I258" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="259" ht="20" customHeight="1">
@@ -19283,7 +19286,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I259" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="260" ht="20" customHeight="1">
@@ -19312,7 +19315,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I260" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="261" ht="20" customHeight="1">
@@ -19341,7 +19344,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I261" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="262" ht="20" customHeight="1">
@@ -19370,7 +19373,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I262" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="263" ht="20" customHeight="1">
@@ -19399,7 +19402,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I263" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="264" ht="20" customHeight="1">
@@ -19428,7 +19431,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I264" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="265" ht="20" customHeight="1">
@@ -19457,7 +19460,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I265" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="266" ht="20" customHeight="1">
@@ -19486,7 +19489,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I266" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="267" ht="20" customHeight="1">
@@ -19515,7 +19518,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I267" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="268" ht="20" customHeight="1">
@@ -19544,7 +19547,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I268" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="269" ht="20" customHeight="1">
@@ -19573,7 +19576,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I269" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="270" ht="20" customHeight="1">
@@ -19602,7 +19605,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I270" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="271" ht="20" customHeight="1">
@@ -19631,7 +19634,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I271" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="272" ht="20" customHeight="1">
@@ -19660,7 +19663,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I272" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="273" ht="20" customHeight="1">
@@ -19689,7 +19692,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I273" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="274" ht="20" customHeight="1">
@@ -19718,7 +19721,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I274" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="275" ht="20" customHeight="1">
@@ -19747,7 +19750,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I275" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="276" ht="20" customHeight="1">
@@ -19776,7 +19779,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I276" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="277" ht="20" customHeight="1">
@@ -19805,7 +19808,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I277" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="278" ht="20" customHeight="1">
@@ -19834,7 +19837,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I278" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="279" ht="20" customHeight="1">
@@ -19863,7 +19866,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I279" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="280" ht="20" customHeight="1">
@@ -19892,7 +19895,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I280" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="281" ht="20" customHeight="1">
@@ -19921,7 +19924,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I281" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="282" ht="20" customHeight="1">
@@ -19950,7 +19953,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I282" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="283" ht="20" customHeight="1">
@@ -19979,7 +19982,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I283" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="284" ht="20" customHeight="1">
@@ -20008,7 +20011,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I284" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="285" ht="20" customHeight="1">
@@ -20037,7 +20040,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I285" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="286" ht="20" customHeight="1">
@@ -20066,7 +20069,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I286" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="287" ht="20" customHeight="1">
@@ -20095,7 +20098,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I287" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="288" ht="20" customHeight="1">
@@ -20124,7 +20127,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I288" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="289" ht="20" customHeight="1">
@@ -20153,7 +20156,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I289" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="290" ht="20" customHeight="1">
@@ -20182,7 +20185,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I290" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="291" ht="20" customHeight="1">
@@ -20211,7 +20214,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I291" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="292" ht="20" customHeight="1">
@@ -20240,7 +20243,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I292" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="293" ht="20" customHeight="1">
@@ -20269,7 +20272,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I293" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="294" ht="20" customHeight="1">
@@ -20298,7 +20301,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I294" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="295" ht="20" customHeight="1">
@@ -20327,7 +20330,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I295" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="296" ht="20" customHeight="1">
@@ -20356,7 +20359,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I296" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="297" ht="20" customHeight="1">
@@ -20385,7 +20388,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I297" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="298" ht="20" customHeight="1">
@@ -20414,7 +20417,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I298" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="299" ht="20" customHeight="1">
@@ -20443,7 +20446,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I299" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="300" ht="20" customHeight="1">
@@ -20472,7 +20475,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I300" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="301" ht="20" customHeight="1">
@@ -20501,7 +20504,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I301" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="302" ht="20" customHeight="1">
@@ -20530,7 +20533,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I302" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="303" ht="20" customHeight="1">
@@ -20559,7 +20562,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I303" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="304" ht="20" customHeight="1">
@@ -20588,7 +20591,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I304" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="305" ht="20" customHeight="1">
@@ -20617,7 +20620,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I305" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="306" ht="20" customHeight="1">
@@ -20646,7 +20649,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I306" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="307" ht="20" customHeight="1">
@@ -20675,7 +20678,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I307" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="308" ht="20" customHeight="1">
@@ -20704,7 +20707,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I308" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="309" ht="20" customHeight="1">
@@ -20733,7 +20736,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I309" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="310" ht="20" customHeight="1">
@@ -20762,7 +20765,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I310" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="311" ht="20" customHeight="1">
@@ -20791,7 +20794,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I311" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="312" ht="20" customHeight="1">
@@ -20820,7 +20823,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I312" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="313" ht="20" customHeight="1">
@@ -20849,7 +20852,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I313" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="314" ht="20" customHeight="1">
@@ -20878,7 +20881,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I314" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="315" ht="20" customHeight="1">
@@ -20907,7 +20910,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I315" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="316" ht="20" customHeight="1">
@@ -20936,7 +20939,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I316" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="317" ht="20" customHeight="1">
@@ -20965,7 +20968,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I317" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="318" ht="20" customHeight="1">
@@ -20994,7 +20997,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I318" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="319" ht="20" customHeight="1">
@@ -21023,7 +21026,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I319" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="320" ht="20" customHeight="1">
@@ -21052,7 +21055,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I320" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="321" ht="20" customHeight="1">
@@ -21081,7 +21084,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I321" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="322" ht="20" customHeight="1">
@@ -21110,7 +21113,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I322" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="323" ht="20" customHeight="1">
@@ -21139,7 +21142,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I323" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="324" ht="20" customHeight="1">
@@ -21168,7 +21171,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I324" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="325" ht="20" customHeight="1">
@@ -21197,7 +21200,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I325" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="326" ht="20" customHeight="1">
@@ -21226,7 +21229,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I326" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="327" ht="20" customHeight="1">
@@ -21255,7 +21258,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I327" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="328" ht="20" customHeight="1">
@@ -21284,7 +21287,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I328" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="329" ht="20" customHeight="1">
@@ -21313,7 +21316,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I329" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="330" ht="20" customHeight="1">
@@ -21342,7 +21345,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I330" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="331" ht="20" customHeight="1">
@@ -21371,7 +21374,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I331" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="332" ht="20" customHeight="1">
@@ -21400,7 +21403,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I332" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="333" ht="20" customHeight="1">
@@ -21429,7 +21432,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I333" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="334" ht="20" customHeight="1">
@@ -21458,7 +21461,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I334" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="335" ht="20" customHeight="1">
@@ -21487,7 +21490,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I335" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="336" ht="20" customHeight="1">
@@ -21516,7 +21519,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I336" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="337" ht="20" customHeight="1">
@@ -21545,7 +21548,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I337" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="338" ht="20" customHeight="1">
@@ -21574,7 +21577,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I338" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="339" ht="20" customHeight="1">
@@ -21603,7 +21606,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I339" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="340" ht="20" customHeight="1">
@@ -21632,7 +21635,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I340" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="341" ht="20" customHeight="1">
@@ -21661,7 +21664,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I341" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="342" ht="20" customHeight="1">
@@ -21690,7 +21693,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I342" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="343" ht="20" customHeight="1">
@@ -21719,7 +21722,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I343" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="344" ht="20" customHeight="1">
@@ -21748,7 +21751,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I344" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="345" ht="20" customHeight="1">
@@ -21777,7 +21780,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I345" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="346" ht="20" customHeight="1">
@@ -21806,7 +21809,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I346" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="347" ht="20" customHeight="1">
@@ -21835,7 +21838,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I347" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="348" ht="20" customHeight="1">
@@ -21864,7 +21867,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I348" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="349" ht="20" customHeight="1">
@@ -21893,7 +21896,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I349" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="350" ht="20" customHeight="1">
@@ -21922,7 +21925,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I350" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="351" ht="20" customHeight="1">
@@ -21951,7 +21954,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I351" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="352" ht="20" customHeight="1">
@@ -21980,7 +21983,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I352" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="353" ht="20" customHeight="1">
@@ -22009,7 +22012,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I353" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="354" ht="20" customHeight="1">
@@ -22038,7 +22041,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I354" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="355" ht="20" customHeight="1">
@@ -22067,7 +22070,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I355" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="356" ht="20" customHeight="1">
@@ -22096,7 +22099,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I356" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="357" ht="20" customHeight="1">
@@ -22125,7 +22128,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I357" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="358" ht="20" customHeight="1">
@@ -22154,7 +22157,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I358" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="359" ht="20" customHeight="1">
@@ -22183,7 +22186,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I359" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="360" ht="20" customHeight="1">
@@ -22212,7 +22215,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I360" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="361" ht="20" customHeight="1">
@@ -22241,7 +22244,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I361" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="362" ht="20" customHeight="1">
@@ -22270,7 +22273,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I362" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="363" ht="20" customHeight="1">
@@ -22299,7 +22302,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I363" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
     <x:row r="364" ht="20" customHeight="1">
@@ -22328,7 +22331,7 @@
         <x:v>Major only</x:v>
       </x:c>
       <x:c r="I364" s="20" t="str">
-        <x:v>Major-specific cohort groups only</x:v>
+        <x:v>Never shared — one major and cohort group</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -22338,7 +22341,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92fefa549b85465a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84d0eb2d9a114f44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22369,7 +22372,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>These lectures may combine majors within a faculty; their tutorials remain separate.</x:v>
+        <x:v>Only lectures may combine majors. Tutorials and labs are always separate for one major and one cohort group.</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -23443,7 +23446,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R023cdd4cb8154382"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8890e2c0f7b945e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23524,12 +23527,12 @@
         <x:v>15 minutes after Periods 1, 2, and 3; 30 minutes after Period 4.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="20" customHeight="1">
-      <x:c r="A11" s="20" t="str">
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="21" t="str">
         <x:v>Shared courses</x:v>
       </x:c>
-      <x:c r="B11" s="20" t="str">
-        <x:v>Shared-course lectures may combine majors; tutorials/labs always remain major-specific.</x:v>
+      <x:c r="B11" s="21" t="str">
+        <x:v>Only lectures may combine majors. Tutorials and labs must be scheduled separately for one major and one cohort group.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="20" customHeight="1">
@@ -23547,7 +23550,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd6dbcfcc6744496"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a8022c310a94f80"/>
   </x:tableParts>
 </x:worksheet>
 </file>